--- a/week3/auto_output/auto_excel/920100_三协电机_auto.xlsx
+++ b/week3/auto_output/auto_excel/920100_三协电机_auto.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_交叉校验" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_股权转让" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2019,4 +2021,206 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>校验类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>批次/时点</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>认购方数量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>合计金额(万元)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>合计股数(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>第1批</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2374.4</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>第2批</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1739.32</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>321.5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>发行前（截至招股说明书签署日）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5310.93</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5310.93</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PDF页码</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>转让日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>转让方</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>受让方</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>转让数量(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>转让价格(元/股)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>转让金额(万元)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>自动化提取暂不支持股权转让Sheet，此Sheet需人工补全。Gold标准中已包含。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>